--- a/анкеты_данные.xlsx
+++ b/анкеты_данные.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11145" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Анкеты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,19 +412,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,94 +480,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Аксенова</t>
+          <t>Авдюхин</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Андрей</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Алексеевна</t>
+          <t>Алевтинович</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>город Тула, ул. Н.Руднева, д.53, кв.33</t>
+          <t>Тульская область, Ясногорский район, г. Ясногорск, ул. Гайдара, д.11, кв.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>430442</t>
+          <t>785118</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Центральном районе</t>
+          <t>МП УФМС России по Тульской области в Ясногорском районе</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>05.06.2013</t>
+          <t>13.12.2017</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>219184</t>
+          <t>214770</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Алешина</t>
+          <t>Аксенова</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ивановна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Тульская область, Ленинский район, дер. Коптево, ул. Садовая, корп.1, кв.1</t>
+          <t>город Тула, ул. Н.Руднева, д.53, кв.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>174266</t>
+          <t>430442</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Ленинском районе</t>
+          <t>ОУФМС России по Тульской области в Центральном районе</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17.02.2010</t>
+          <t>05.06.2013</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,49 +577,49 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>024303</t>
+          <t>219184</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ашихмина</t>
+          <t>Алешина</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Елена</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Львовна</t>
+          <t>Ивановна</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>город Тула, ул. М.Горького, д.14, кв.310</t>
+          <t>Тульская область, Ленинский район, дер. Коптево, ул. Садовая, корп.1, кв.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>549554</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Зареченском районе</t>
+          <t>ОУФМС России по Тульской области в Ленинском районе</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15.10.2014</t>
+          <t>17.02.2010</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -632,113 +629,101 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>219939</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>12.05.2025</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+          <t>024303</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Барахова</t>
+          <t>Анферова</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Раиса</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Дмитриевна</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>город Тула, ул. Галкина, д.221</t>
+          <t>Тульская область, Щекинский район, д. Лукино, ул. Новая, д.2, кв.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>197851</t>
+          <t>270527</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Зареченском районе</t>
+          <t>ОУФМС России по Тульской области в Щекинском районе</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>07.03.2017</t>
+          <t>11.05.2011</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>219242</t>
+          <t>758025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Баталина</t>
+          <t>Ашихмина</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Алексеевна</t>
+          <t>Львовна</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>город Тула, ул. 4-й Лихвинский проезд, д.8А</t>
+          <t>город Тула, ул. М.Горького, д.14, кв.310</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>228285</t>
+          <t>549579</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>ОУФМС России по Тульской области в Зареченском районе</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>04.03.2024</t>
+          <t>15.10.2014</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -748,205 +733,205 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>234234</t>
+          <t>219939</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бехтеев</t>
+          <t>Барахова</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Виктор</t>
+          <t>Ирина</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>г. Тула, ул. Калинина, д. 26, корп. 2, кв. 43</t>
+          <t>город Тула, ул. Галкина, д. 221</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>524663</t>
+          <t>197851</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>УВД Пролетарского района города Тулы</t>
+          <t>ОУФМС России по Тульской области в Зареченском районе</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>26.03.2025</t>
+          <t>07.03.2017</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>234322</t>
+          <t>219242</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Блынду</t>
+          <t>Баталина</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Анжелика</t>
+          <t>Мария</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Валерьевна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Тульская область, г. Ясногорск, ул. Шиловская, д.13</t>
+          <t>город Тула, ул. 4-й Лихвинский проезд, д.8А</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>601656</t>
+          <t>228285</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>МП УФМС России по Тульской области в Ясногорском районе</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>15.10.2010</t>
+          <t>04.03.2024</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Е</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>676787</t>
+          <t>431178</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Бордунова</t>
+          <t>Бехтеев</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Зинаида</t>
+          <t>Виктор</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ивановна</t>
+          <t>Иванович</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Тульская область, Плавский район, ст. Горбачево, д.2, кв.2</t>
+          <t>г. Тула, ул. Калинина, д. 26, корп. 2, кв. 43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>571198</t>
+          <t>524663</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ТП УФМС по Тульской области в Плавском районе</t>
+          <t>УВД Пролетарского района города Тулы</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20.03.2015</t>
+          <t>26.03.2002</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>024406</t>
+          <t>757700</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Бочаров</t>
+          <t>Благов</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Геннадий</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Викторович</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Тульская область, Киреевский район, г.Липки, ул. Красногвардейская, д.15, кв.1</t>
+          <t>город Тула, ул. Волкова, д.7, кв. 44</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>892766</t>
+          <t>078520</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>ТП в МКН Кировский ОУФМС России по Тульской области в Пролетарском районе города Тулы</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.07.2019</t>
+          <t>18.12.2008</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -956,49 +941,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>000000</t>
+          <t>276329</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Воронов</t>
+          <t>Блынду</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Владимир</t>
+          <t>Анжелика</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Анатольевич</t>
+          <t>Валерьевна</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>г. Липецк, ул. Советская, д.68, кв.169</t>
+          <t>Тульская область, г. Ясногорск, ул. Шиловская, д.13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>415434</t>
+          <t>601656</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
+          <t>МП УФМС России по Тульской области в Ясногорском районе</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>29.03.2013</t>
+          <t>15.10.2015</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1008,101 +993,101 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>219023</t>
+          <t>220098</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Димитриев</t>
+          <t>Бордунова</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Зинаида</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Васильевич</t>
+          <t>Ивановна</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Тульская область, пос. Советский, ул. Шоссейная, д.7,     кв. 1</t>
+          <t>Тульская область, Плавский район, ст. Горбачево, д.2, кв.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>456891</t>
+          <t>571198</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ТП УФМС России по Тульской области в Плавском районе</t>
+          <t>ТП УФМС по Тульской области в Плавском районе</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.12.2013</t>
+          <t>20.03.2015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>778346</t>
+          <t>024406</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ефимова</t>
+          <t>Бочаров</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Сергеевна</t>
+          <t>Леонидович</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Тульская область, Ленинский район, д. Кураково, д.44</t>
+          <t>Тульская область, Киреевский район, г.Липки, ул. Красногвардейская, д.15, кв.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>532333</t>
+          <t>892766</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ленинским РОВД Тульской области</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13.01.2002</t>
+          <t>10.07.2019</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1112,101 +1097,101 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>758474</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Звездилина</t>
+          <t>Воронов</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Надежда</t>
+          <t>Владимир</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Яковлевна</t>
+          <t>Анатольевич</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>город Тула, улица Дмитрия Ульянова, д.20, кв. 11</t>
+          <t>г. Липецк, ул. Советская, д.68, кв.169</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>770599</t>
+          <t>415434</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ОВД Советского района города Тулы</t>
+          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20.11.2002</t>
+          <t>29.03.2013</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>990216</t>
+          <t>219023</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ибрагимова</t>
+          <t>Гогия</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Гузалия</t>
+          <t>Анатолий</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Дулкарамовна</t>
+          <t>Гогликович</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Тульская область, Плавский район, ст. Горбачево, ул. Горького, д.48, кв.9</t>
+          <t>г. Тула, ул. Металлургов, д.76-а, кв.21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>649798</t>
+          <t>055760</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Плавским РОВД Тульской области</t>
+          <t>Кировским отделением милиции УВД Пролетарского района города Тулы</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.02.2005</t>
+          <t>04.02.2003</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1216,39 +1201,39 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>432843</t>
+          <t>432674</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Иванова</t>
+          <t>Димитриев</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Васильевич</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Тульская область, Плавский район, пос. Советский, ул. Шоссейная, д.5, кв. 4</t>
+          <t>Тульская область, пос. Советский, ул. Шоссейная, д.7,     кв. 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>944330</t>
+          <t>456891</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1258,59 +1243,59 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.11.2007</t>
+          <t>11.12.2013</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>А</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>219654</t>
+          <t>778343</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Исаева</t>
+          <t>Ефимова</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Тамара</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Сергеевна</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Тульская область, с. Воскресенское, ул. Школьная, д.1, кв.45</t>
+          <t>Тульская область, Ленинский район, д. Кураково, д.44</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>204817</t>
+          <t>532333</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Дубенским РОВД Тульской области</t>
+          <t>Ленинским РОВД Тульской области</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17.12.2001</t>
+          <t>13.01.2004</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1320,49 +1305,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>782735</t>
+          <t>757867</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Калинина</t>
+          <t>Жучкова</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ольга</t>
+          <t>Людмила</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Евгеньевна</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Тульская область, пос. Иншинский, д.1, кв.16</t>
+          <t>город Тула, ул. Красноармейский проспект, д.48, кв.32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>631753</t>
+          <t>432417</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ленинским РОВД Тульской области</t>
+          <t>Привокзальным РОВД Тулы</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>02.12.2004</t>
+          <t>30.01.2002</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1372,101 +1357,101 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>893115</t>
+          <t>891726</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Колоскова</t>
+          <t>Звездилина</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Любовь</t>
+          <t>Надежда</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Яковлевна</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>г. Тула, ул. Мезенцева, д.38, кв.39</t>
+          <t>город Тула, улица Дмитрия Ульянова, д.20, кв. 11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>926734</t>
+          <t>770599</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Центральном районе города Тулы</t>
+          <t>ОВД Советского района города Тулы</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>24.07.2007</t>
+          <t>20.11.2002</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>207123</t>
+          <t>990212</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Комаров</t>
+          <t>Зуева</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Валерий</t>
+          <t>Елена</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>г. Тула, ул. Пушкинская, д.57, кв. 203</t>
+          <t>Тульская область, Ленинский район, д. Сеженские выселки, д.31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>843839</t>
+          <t>805321</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ОВД Советского района города Тулы</t>
+          <t>УВД Пролетарского района города Тулы</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>02.12.2002</t>
+          <t>14.03.2006</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1476,257 +1461,257 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>219994</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Комракова</t>
+          <t>Ибрагимова</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Наталья</t>
+          <t>Гузалия</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Евгеньевна</t>
+          <t>Дулкарамовна</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>г. Тула, ул. 2-й проезд Металлургов, д.6, кв.50</t>
+          <t>Тульская область, Плавский район, ст. Горбачево, ул. Горького, д.48, кв.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>977764</t>
+          <t>649798</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ТП В МКН Кировский ОУФМС России по Тульской области в пролетарском районе Тулы</t>
+          <t>Плавским РОВД Тульской области</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27.12.2007</t>
+          <t>17.02.2005</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>214967</t>
+          <t>432843</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Кулаков</t>
+          <t>Иванова</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Павел</t>
+          <t>Татьяна</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Евгеньевич</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Тульская область, Киреевский район, п. Шварцевский, ул. Ленина, д.14, кв.74</t>
+          <t>Тульская область, Плавский район, пос. Советский, ул. Шоссейная, д.5, кв. 4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>141403</t>
+          <t>944330</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>ТП УФМС России по Тульской области в Плавском районе</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>15.11.2022</t>
+          <t>23.11.2007</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>273481</t>
+          <t>219659</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Кученкова</t>
+          <t>Исаева</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Тамара</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Валерьевна</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>г. Тула, д. Старое Басово, д.29а</t>
+          <t>Тульская область, с. Воскресенское, ул. Школьная, д.1, кв.45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>705876</t>
+          <t>204817</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Привокзальном районе</t>
+          <t>Дубенским РОВД Тульской области</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>20.12.2016</t>
+          <t>17.12.2001</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>431522</t>
+          <t>782735</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Кушнарёва</t>
+          <t>Калинина</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Галина</t>
+          <t>Ольга</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Андреевна</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Тульская область, г. Киреевск, ул. Комарова, д.19, кв.68</t>
+          <t>Тульская область, пос. Иншинский, д.1, кв.16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>864734</t>
+          <t>631753</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>Ленинским РОВД Тульской области</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18.02.2019</t>
+          <t>02.12.2004</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>А</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>214543</t>
+          <t>893115</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Лесневский</t>
+          <t>Колоскова</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Александр</t>
+          <t>Любовь</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Валериевич</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Тульская область, Киреевский район, п. Бородинский, ул. Пушкина, д.11, кв. 77</t>
+          <t>г. Тула, ул. Мезенцева, д.38, кв.39</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>297506</t>
+          <t>926734</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Бородинским отделением милиции Киреевского РОВД Тульской области</t>
+          <t>ОУФМС России по Тульской области в Центральном районе города Тулы</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>21.05.2003</t>
+          <t>24.07.2007</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1736,49 +1721,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>220145</t>
+          <t>207487</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Макарова</t>
+          <t>Комаров</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Валерий</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Тульская область, Киреевский район, г. Болохово, ул. Соловцова, д.19а, кв.44</t>
+          <t>г. Тула, ул. Пушкинская, д.57, кв. 203</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>737500</t>
+          <t>843839</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
+          <t>ОВД Советского района города Тулы</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>06.07.2017</t>
+          <t>02.12.2002</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1788,153 +1773,153 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>220542</t>
+          <t>219969</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Максимова-Маляр</t>
+          <t>Комракова</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Нелли</t>
+          <t>Наталья</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Александровна</t>
+          <t>Евгеньевна</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Донецкая Народная Республика, г. Краматорск, ул. Академическая, д.84, кв.35</t>
+          <t>г. Тула, ул. 2-й проезд Металлургов, д.6, кв.50</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>149663</t>
+          <t>977764</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ГУ МВД России по Ростовской области</t>
+          <t>ТП В МКН Кировский ОУФМС России по Тульской области в пролетарском районе Тулы</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17.11.2022</t>
+          <t>27.12.2007</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>432465</t>
+          <t>214967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Малахина</t>
+          <t>Кулаков</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ирина</t>
+          <t>Павел</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Станиславовна</t>
+          <t>Евгеньевич</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Нижегородская область, Починковский район, с. Ильинское, ул. Новая, д.23</t>
+          <t>Тульская область, Киреевский район, п. Шварцевский, ул. Ленина, д.14, кв.74</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>273423</t>
+          <t>141403</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ОУФМС России по Нижегородской области в Починковском районе</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20.03.2009</t>
+          <t>15.11.2022</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>431674</t>
+          <t>273481</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Малдаховская</t>
+          <t>Кученкова</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Галина</t>
+          <t>Татьяна</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Валерьевна</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>город Тула, Скуратовский микрорайон, д.8, кв.58</t>
+          <t>г. Тула, д. Старое Басово, д.29а</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>966666</t>
+          <t>705876</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ТП В ПГТ Скуратовский ОУФМС России по Тульской области в Центральном районеТулы</t>
+          <t>ОУФМС России по Тульской области в Привокзальном районе</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16.11.2007</t>
+          <t>20.12.2016</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1944,101 +1929,101 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>024252</t>
+          <t>431522</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Матвеев</t>
+          <t>Кушнарёва</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Галина</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Александрович</t>
+          <t>Андреевна</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>г. Тула, пос. Скуратовский, ул. Треугольная, д.4</t>
+          <t>Тульская область, г. Киреевск, ул. Комарова, д.19, кв.68</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>327859</t>
+          <t>864706</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Чернским РОВД Тульской области</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>03.12.2007</t>
+          <t>18.02.2019</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>336534</t>
+          <t>218992</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Медведков</t>
+          <t>Лесневский</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Василий</t>
+          <t>Александр</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Степанович</t>
+          <t>Валериевич</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>город Тула, ул.Революции, д.12, кв.111</t>
+          <t>Тульская область, Киреевский район, п. Бородинский, ул. Пушкина, д.11, кв. 77</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>036977</t>
+          <t>297506</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>Бородинским отделением милиции Киреевского РОВД Тульской области</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12.07.2021</t>
+          <t>21.05.2003</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2048,101 +2033,101 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>024345</t>
+          <t>220106</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Моисейчева</t>
+          <t>Макарова</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Людмила</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Алексеевна</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>город Москва, ул. Подольская, д.1, кв. 119, ком. 2</t>
+          <t>Тульская область, Киреевский район, г. Болохово, ул. Соловцова, д.19а, кв.44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>208415</t>
+          <t>737500</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ОВД Советского района города Тулы</t>
+          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22.08.2001</t>
+          <t>06.07.2017</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>530530</t>
+          <t>220542</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Москалева</t>
+          <t>Максимова-Маляр</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Марина</t>
+          <t>Нелли</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>г. Тула, ул. Новомосковская, д.1, кв.10</t>
+          <t>Донецкая Народная Республика, г. Краматорск, ул. Академическая, д.84, кв.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>149663</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Отделением в Советском районе ОУФМС РФ по Тульской области</t>
+          <t>ГУ МВД России по Ростовской области</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20.10.2010</t>
+          <t>17.11.2022</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2152,49 +2137,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>431466</t>
+          <t>432465</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Надирова</t>
+          <t>Малахина</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Марина</t>
+          <t>Ирина</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Васильевна</t>
+          <t>Станиславовна</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>город Тула, ул. Тимирязева, д.101, корп. 4, кв. 26</t>
+          <t>Нижегородская область, Починковский район, с. Ильинское, ул. Новая, д.23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>031321</t>
+          <t>273423</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Центральном районе города Тула</t>
+          <t>ОУФМС России по Нижегородской области в Починковском районе</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18.06.2008</t>
+          <t>20.03.2009</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2204,66 +2189,66 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>431197</t>
+          <t>431674</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Находнов</t>
+          <t>Малдаховская</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Алексей</t>
+          <t>Галина</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Игоревич</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>город Тула, ул. Фрунзе, д.23, кв.45</t>
+          <t>город Тула, Скуратовский микрорайон, д.8, кв.58</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>245194</t>
+          <t>966666</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>ТП В ПГТ Скуратовский ОУФМС России по Тульской области в Центральном районеТулы</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01.04.2024</t>
+          <t>16.11.2007</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>772477</t>
+          <t>024252</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Находнов</t>
+          <t>Матвеев</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2273,64 +2258,64 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Валентинович</t>
+          <t>Александрович</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>г. Тула, ул. Революции, д.24, кв.50</t>
+          <t>г. Тула, пос. Скуратовский, ул. Треугольная, д.4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>768987</t>
+          <t>327859</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>ОВД Советского раона города Тулы</t>
+          <t>Чернским РОВД Тульской области</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21.02.2006</t>
+          <t>03.12.2007</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>432444</t>
+          <t>336534</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Перегудов</t>
+          <t>Медведев</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Анатолий</t>
+          <t>Виктор</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Иванович</t>
+          <t>Петрович</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>город Тула, ул. Сойфера, д.9, кв.101</t>
+          <t>город Тула, пос. Хомяково, ул. Хомяковская, д.13, кв.10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2340,59 +2325,59 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>250663</t>
+          <t>331151</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>УВД Центрального района города Тулы</t>
+          <t>Зареченским РОВД города Тулы</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>16.10.2003</t>
+          <t>21.08.2003</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>646135</t>
+          <t>203577</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Плиско</t>
+          <t>Медведков</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Василий</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Федорович</t>
+          <t>Степанович</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Тульская область, пос. Дубна, ул. Фрунзе, д.37</t>
+          <t>город Тула, ул.Революции, д.12, кв.111</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>820163</t>
+          <t>036977</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2402,59 +2387,59 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>05.10.2018</t>
+          <t>12.07.2021</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>344914</t>
+          <t>024345</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Полосина</t>
+          <t>Моисейчева</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Анна</t>
+          <t>Людмила</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Владиславовна</t>
+          <t>Алексеевна</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Тульская область, Киреевский район, г. Киреевск, ул. Заречная, д.6, кв.18</t>
+          <t>город Москва, ул. Подольская, д.1, кв. 119, ком. 2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>605180</t>
+          <t>208415</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ТП  в Липки ОУФМС России по Тульской области в Киреевском районе</t>
+          <t>ОВД Советского района города Тулы</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21.12.2015</t>
+          <t>22.08.2001</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2464,101 +2449,101 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>511875</t>
+          <t>530530</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Портной</t>
+          <t>Морозова</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Виктор</t>
+          <t>Марина</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Яковлевич</t>
+          <t>Александровна</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>г. Тула, Ф.Энгельса, д.137, кв.53</t>
+          <t>Тульская область, Щекинский район, д. Лукино, ул. Куприянова, д.62</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>098217</t>
+          <t>322284</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>УВД Центрального района Тулы</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10.06.2003</t>
+          <t>30.04.2025</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>780944</t>
+          <t>432860</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Рассадин</t>
+          <t>Москалева</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Марина</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Игоревич</t>
+          <t>Николаевна</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>город Тула, ул. Первомайская, д.14а, кв. 37</t>
+          <t>г. Тула, ул. Новомосковская, д.1, кв.10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>013173</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>Отделением в Советском районе ОУФМС РФ по Тульской области</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12.02.2021</t>
+          <t>20.10.2010</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2568,49 +2553,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>431200</t>
+          <t>431466</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Рустамова</t>
+          <t>Надирова</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Светлана</t>
+          <t>Марина</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Борисовна</t>
+          <t>Васильевна</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>город Тула, ул. Мезенцева, д.44, корп.3, кв.36</t>
+          <t>город Тула, ул. Тимирязева, д.101, корп. 4, кв. 26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>752532</t>
+          <t>031321</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Центральном районе</t>
+          <t>ОУФМС России по Тульской области в Центральном районе города Тула</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>16.08.2017</t>
+          <t>18.06.2008</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2620,29 +2605,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>431712</t>
+          <t>431197</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Сабуров</t>
+          <t>Находнов</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Эркин</t>
+          <t>Алексей</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Хатамбайевич</t>
+          <t>Игоревич</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Тульская облоасть, Кимовский район, д. Ренево, д.13</t>
+          <t>город Тула, ул. Фрунзе, д.23, кв.45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2652,7 +2637,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>201158</t>
+          <t>245194</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2662,319 +2647,319 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>23.08.2023</t>
+          <t>01.04.2024</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>432229</t>
+          <t>772477</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Садыков</t>
+          <t>Находнов</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Марат</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Шарифович</t>
+          <t>Валентинович</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Тульская область, Плавский район, пос. Молочные дворы, ул. Садовая, д.3, кв. 11</t>
+          <t>г. Тула, ул. Революции, д.24, кв.50</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>755964</t>
+          <t>768987</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ТП УФМС России по Тульской области в Плавском районе</t>
+          <t>ОВД Советского раона города Тулы</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>06.09.2017</t>
+          <t>21.02.2006</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>460335</t>
+          <t>432444</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Севостьянова</t>
+          <t>Перегудов</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Елизавета</t>
+          <t>Анатолий</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ивановна</t>
+          <t>Иванович</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Тульская область, г. Ясногорск, ул. П.Смидовича, д.33, кв.1</t>
+          <t>город Тула, ул. Сойфера, д.9, кв.101</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>223346</t>
+          <t>250663</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Орджоникидзевским РУВД Уфы Респ. Башкортостан</t>
+          <t>УВД Центрального района города Тулы</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>07.05.2007</t>
+          <t>16.10.2003</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>990600</t>
+          <t>646135</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Сивакова</t>
+          <t>Плиско</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Татьяна</t>
+          <t>Сергей</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Михайловна</t>
+          <t>Федорович</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>г. Тула, ул. М.Горького, д.10, кв.41</t>
+          <t>Тульская область, пос. Дубна, ул. Фрунзе, д.37</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>374104</t>
+          <t>820163</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Зареченским РОВДТулы</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>14.01.2002</t>
+          <t>05.10.2018</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>431648</t>
+          <t>344914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Сидоров</t>
+          <t>Полосина</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Игорь</t>
+          <t>Анна</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Павлович</t>
+          <t>Владиславовна</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>г.Тула, ул. Клары Цеткин, д.5, корп. 3, кв.15</t>
+          <t>Тульская область, Киреевский район, г. Киреевск, ул. Заречная, д.6, кв.18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>554610</t>
+          <t>605180</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Косогорским отделением милиции Привокзального РОВД Тулы</t>
+          <t>ТП  в Липки ОУФМС России по Тульской области в Киреевском районе</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>02.02.2005</t>
+          <t>21.12.2015</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>431491</t>
+          <t>511875</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Соколова</t>
+          <t>Портной</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Галина</t>
+          <t>Виктор</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Яковлевич</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>город  Тула, ул. Красноармейский проспект, д.38, кв. 70</t>
+          <t>г. Тула, Ф.Энгельса, д.137, кв.53</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>654227</t>
+          <t>098217</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Щекинским РУВД Тульской области</t>
+          <t>УВД Центрального района Тулы</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25.03.2005</t>
+          <t>10.06.2003</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>431543</t>
+          <t>780944</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Сопова</t>
+          <t>Потапова</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Людмила</t>
+          <t>Нина</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Викторовна</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Московская область, г.о. Красногорск, д. Путилково, ул. Спасо-Тушинский б-р, д.8, кв. 552</t>
+          <t>город Тула, ТСНСТ "Приволье", ул. 93-М</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>737096</t>
+          <t>587619</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Отделом УФМС России по Тульской области в Пролетарском районе</t>
+          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>21.06.2017</t>
+          <t>26.05.2015</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2984,49 +2969,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>219233</t>
+          <t>431486</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Сорокина</t>
+          <t>Рассадин</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Лидия</t>
+          <t>Игорь</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Николаевна</t>
+          <t>Игоревич</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>город Тула, ул. Мезенцева, д.44, корп.4, кв.128</t>
+          <t>город Тула, ул. Первомайская, д.14а, кв. 37</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>535172</t>
+          <t>013173</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>ОУФМС России по Тульской области в Привокзальном районе</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>04.09.2014</t>
+          <t>12.02.2021</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3036,49 +3021,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>432461</t>
+          <t>431200</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Строчков</t>
+          <t>Рустамова</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Сергей</t>
+          <t>Светлана</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Константинович</t>
+          <t>Борисовна</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>г. Тула, ул.Клюева д.12, кв.10</t>
+          <t>город Тула, ул. Мезенцева, д.44, корп.3, кв.36</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>801923</t>
+          <t>752532</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>УВД города Пскова</t>
+          <t>ОУФМС России по Тульской области в Центральном районе</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17.07.2005</t>
+          <t>16.08.2017</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3088,267 +3073,5229 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>024368</t>
+          <t>431712</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Троицкий</t>
+          <t>Сабуров</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Юрий</t>
+          <t>Эркин</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Леонидович</t>
+          <t>Хатамбайевич</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Тульская область, Чернский район, с. Лужны, ул. Центральная, д.13, кв. 1</t>
+          <t>Тульская облоасть, Кимовский район, д. Ренево, д.13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>191144</t>
+          <t>201158</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ТП УФМС России по Тульской области в Чернском районе</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>04.03.2010</t>
+          <t>23.08.2023</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>990600</t>
+          <t>432229</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Федотов</t>
+          <t>Садыков</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Геннадий</t>
+          <t>Марат</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Владимирович</t>
+          <t>Шарифович</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Тульская область, п. Шатск, ул. Садовая, д.9, кв.39</t>
+          <t>Тульская область, Плавский район, пос. Молочные дворы, ул. Садовая, д.3, кв. 11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>856905</t>
+          <t>755964</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>ТП УФМС России по Тульской области в Плавском районе</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>21.01.2019</t>
+          <t>06.09.2017</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>А</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>432513</t>
+          <t>460335</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Хомяков</t>
+          <t>Сандакова</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Николай</t>
+          <t>Оксана</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Петрович</t>
+          <t>Владимировна</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Тульская область, Ясногорский район, поселок Ревякино, ул. Клубная, д.10, кв.14</t>
+          <t>Тульская область, Плавский район, с. Камынино, ул. Мира, д.20, кв.1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>206460</t>
+          <t>274863</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ТП УФМС России по Тульской области в Ясногорском районе</t>
+          <t>УМВД России по Тульской области</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14.07.2010</t>
+          <t>01.08.2024</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Г</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>471058</t>
+          <t>220421</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Эзау</t>
+          <t>Севостьянова</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Мария</t>
+          <t>Елизавета</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Евгеньевна</t>
+          <t>Ивановна</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Тульская область, г. Плавск, ул. Заводская, д.44, кв.3</t>
+          <t>Тульская область, г. Ясногорск, ул. П.Смидовича, д.33, кв.1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>916961</t>
+          <t>223346</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>УМВД России по Тульской области</t>
+          <t>Орджоникидзевским РУВД Уфы Респ. Башкортостан</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>11.10.2019</t>
+          <t>07.05.2007</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>В</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>219736</t>
+          <t>990600</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>фывфвфВ</t>
+          <t>Сивакова</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>Татьяна</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Михайловна</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. М.Горького, д.10, кв.41</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>374104</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Зареченским РОВДТулы</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>14.01.2002</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>431648</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Сидоров</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Игорь</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Павлович</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>г.Тула, ул. Клары Цеткин, д.5, корп. 3, кв.15</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>554610</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Косогорским отделением милиции Привокзального РОВД Тулы</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>02.02.2005</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>431491</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Смирнов</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>город Тула, ул. Чапаева, д. 38, кв. 29</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>716315</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в Пролетарском районе</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>06.03.2017</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>432624</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Соколова</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Галина</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>город  Тула, ул. Красноармейский проспект, д.38, кв. 70</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>654227</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Щекинским РУВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>25.03.2005</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>431543</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Сопова</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Московская область, г.о. Красногорск, д. Путилково, ул. Спасо-Тушинский б-р, д.8, кв. 552</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>737096</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России по Тульской области в Пролетарском районе</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>21.06.2017</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>219233</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Сорокина</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Лидия</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>город Тула, ул. Мезенцева, д.44, корп.4, кв.128</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>535172</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в Привокзальном районе</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>04.09.2014</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>432461</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Строчков</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Сергей</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Константинович</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>г. Тула, ул.Клюева д.12, кв.10</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>5804</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>801923</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>УВД города Пскова</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>17.07.2005</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Г</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>123124</t>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>024368</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Товмасян</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Аракел</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Грантович</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Тульская область, Арсеньевский район, пос. Арсеньево, ул. 22 декабря, д.7а</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>222266</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ТП УФМС России по Тульской области в Арсеньевском районе</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>23.11.2010</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>402489</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Троицкий</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Юрий</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Леонидович</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Тульская область, Чернский район, с. Лужны, ул. Центральная, д.13, кв. 1</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>191144</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ТП УФМС России по Тульской области в Чернском районе</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>04.03.2010</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>990600</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Трушина</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Любовь</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Станиславовна</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Тульская область, Щекинский район, д. Лукино, ул. Новая, д.5, кв. 2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>319441</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в Щекинском районе</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>09.11.2011</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>432961</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Федотов</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Геннадий</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Тульская область, п. Шатск, ул. Садовая, д.9, кв.39</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7018</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>856905</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>21.01.2019</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>432513</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Анферова</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Раиса</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Дмитриевна</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Тульская область, Щекинский район, д. Лукино, ул. Новая, д.2, кв.12</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>270527</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в Щекинском районе</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>11.05.2011</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>758025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Хахалин</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Степанович</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>город Тула, СНТ "Медик", д.24</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>7011</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>297651</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ТП в городе Болохово ОУФМС России по Тульской области в Киреевском районе</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>08.08.2011</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>431254</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Хомяков</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Николай</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Петрович</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Тульская область, Ясногорский район, поселок Ревякино, ул. Клубная, д.10, кв.14</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>206460</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ТП УФМС России по Тульской области в Ясногорском районе</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>14.07.2010</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>471058</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Шахкян</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Амаля</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Гарники</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Тульская область, пос. Теплое, ул. Привокзальная, д.17</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>028418</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ТП УФМС России по Тульской области в Тепло-Огаревском районе</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>10.10.2008</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>523062</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Шведова</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Светлана</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Вячеславовна</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>город Тула, ул. Кутузова, д.88а, кв.46</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>324626</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Кировским отделом милиции УВД Пролетарского района города Тулы</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>25.09.2003</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>431487</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Эзау</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Евгеньевна</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Тульская область, г. Плавск, ул. Заводская, д.44, кв.3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>7019</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>916961</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>11.10.2019</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>219736</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Яковлев</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Альберт</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>город Тула, ул. Л.Чайкиной, д.6</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>775378</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>УВД Центрального района города Тулы</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>06.12.2005</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>432656</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Агапова</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Наталья</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Владимировна</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Тульская обл. Ясногорский  р-он п. Ревякино ул. Мира д. 2 кв. 45</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>7021</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>036147</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>16.06.2021</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>100612</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Аникеева</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Нина</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Фроловна</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>г. Тула ул. Марата д. 26 кв. 143</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>642299</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>УВД Пролетарского р-на гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>07.12.2004</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>990679</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Афанасьев</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Иванович</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Тульская обл., Ленинский р-он, пос. Плеханово, ул. Луговая, д. 3 А</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>350169</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ОВД Ленинского р-на Тульской области</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>09.11.2001</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>990716</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Афонин</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>г. Тула , ул. Декабристов, д. 73</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>805169</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>УВД Пролетарского Районагор. Тулы</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>04.09.2002</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>010128</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>АФОНИН</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ОЛЕГ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>НИКОЛАЕВИЧ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ТУЛЬСКАЯ ОБЛ. ЯСНОГОРСКИЙ Р-ОН ПГТ РЕВЯКИНО УЛ. ПОЛВАЯ Д.31/18</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>552227</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ТП УФМС РОССИИ П ТУЛЬСКОЙ ОБЛАСТИ В ЯСНОГОРСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>11.03.2015</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>446711</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Белецкий</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Игорь</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Юрьевич</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Купцов Гречихиных. д. 12, кв. 218</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>7021</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>015344</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>10.03.2021</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>431613</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Блохина</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Любовь</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ивановна</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Тула, Ак. Павлова, д.31,</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>695136</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>УВД Центрального района Тулы</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>18.05.2005</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>219013</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Братчиков</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Тульская обл,Ленинский р-он, с. Архангельское д. 31</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>401966</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ОУФМС Россиипо Тульской Области в Пролетарском районе</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>27.12.2012</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>432498</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Бухарова</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Наталия</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Владимировна</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>г. Тула ул. Максимовского д. 9 кв 76</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>733291</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД города Тулы</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>11.11.2005</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>431641</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ВОЛОДИН</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>АЛЕКСАНДР</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>СЕРГЕЕВИЧ</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>г. Тула ул. К. Маркса д. 37/13</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>516128</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>УВД ПРОЛЕТАРСКОГО РАЙОНА ГОР</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>894480</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Волошкин</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Тула, ул. Макаренко, д. 17, кв.90</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>049487</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ОВД  Советского района гор Тулы</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>20.06.2003</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>207484</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Вольман</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Тульская обл. г Киреевск ул. Коморова д. 15 кв 82</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>533175</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Киреевским РОВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>01.04.2002</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>273390</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Воробьев</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Тула. ул. Галкина 10</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>7025</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>353438</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>31.10.2025</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>432625</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Вохмянин</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Данилович</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Тулская обл., Дубенский р-он, МУ Поресенское, с. Опочня, ул. Фестивальная, д. 22</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>148287</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ТП УФМИ России по Тульской области в Дубенском районе</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>25.11.2009</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>219584</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Галикеева</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Надежда</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Тульскакя обл., Чернский район, пос. Степной, ул. Молодежная , д. 2</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>815289</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ОВД Чернского района Тульской области</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>12.05.2006</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>220413</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Гаража</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Надежда</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Павловна</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Тульская обл. Чернский район с Малое Скуратово ул. Мира д. 9</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>713448</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Чернским РОВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>18.07.2005</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>220425</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Гончарова</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Галина</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Р.Зорге, д. 191. кв 2 к.4</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>914338</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>27.11.2002</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>431720</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Гордеева</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Михайловна</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Тула ул. Октябрьская д. 10 кв 26</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>444667</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Отделением УФМС России по Тульской области в зареченском районе</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>15.07.2013</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>776215</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Давыдова</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ирина</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Вячеславовна</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>г. Тула , ул. Рудная, д. 10</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>175152</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ТП В МКН Кировский ОУФМС России по Тульской области в Пролетарском районе города Тулы</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>16.04.2010</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>462950</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Демкина</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ирина</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Васильевна</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Тульская обл. г. Щекино ул. Емельянова, д. 36 в. 42</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>878962</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Щекинским  РУВД Тултской обл.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>30.09.2002</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>530671</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Денисюк</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Антонович</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>г. Тула , ул. Октябрьская, д. 87, кв 29</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>166552</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Зареченский РОВД гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>25.07.2003</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>457511</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Дзюба</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Васильевич</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>г.Тула, пос. Октябрьский, пр 8-й, д. 47</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>278614</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>отделение в зареченском районе отдела УФМС России по Тульской области в Туле</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>16.06.2011</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>219957</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Добрынина</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Вениаминовна</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Тула пр. Ленина д. 147 кор 3 кв. 3</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>670802</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>УВД Центрального района гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>42.07.2002</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>517327</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ЕГОРИЧЕВ</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>НИКОЛАЙ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ИВАНОВИЧ</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Тульская область, Ясногорский район, д. Федяшева, ул. Южная, д. 10,кв. 2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>851013</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ОВД Ясногорского района Тульской области</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>09.11.2006</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>891574</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Елина</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Марина</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Евгеньевна</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Металлургов, д. 43В, кв.37</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>148742</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ОУФМС РОССИИ ПО ТУЛЬСКОЙ ОБЛАСТИ В ПРОЛЕТАРСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>25.09.2009</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>894236</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Емельянова</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Васильевна</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Тульская область, г. Новомосковск, ул. Орджоникидзе,д. 3 Г,кв. 8</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>011427</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ТП УФМС России по Тульской области в Воловском районе</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>05.06.2008</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>432073</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Ефимов</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Геннадьевич</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Тульская область, Ленинский район, дер. Марьино, д. 78 А</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>876242</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ленинским РОВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>11.10.2006</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>875691</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Жаров</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Петрович</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>тульская обл,  Чернский район, п. Скуратовский, ул. Привокзальная д. 56</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>782806</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>УМВД России по Мурмонской области</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>26.01.2023</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>431884</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Завальнев</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Вячеслав</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Викторович</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Тульская область Ленинский Район п. Иншинский д. 4 "Б" кв.86</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>112595</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России по Тульской области в Щекинском районе</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>06.05.2009</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>067245</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Зыбин</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Евгений</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Тульская область, г. Киреевсе, ул. Л. Толстого, д. 16, кв.51</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>973193</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>УМВД РОССИИ ПО ТУЛЬСКОЙ ОБЛАСТИ</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>28.07.2020</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>516026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Иванова</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Татьяна</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>г.Тула, М.Горького, д. 33 А, кв. 31</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>160760</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ОУФМС РОССИИ ПО ТУЛЬСКОЙ ОБЛАСТИ В ЗАРЕЧЕНСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>04.03.2010</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>431458</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Калинина</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Алевтина</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Павловна</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>г. Тула ул Рязанская д.26 кор 2 кв 21</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>578962</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>05.01.2004</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>431532</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Калитай</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Парфеновна</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Тульская область г. Киреевск ул. Тесакова д. 2А кв. 11 ком 9</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>477211</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Отделением УФМС России по Тульской области в Киреевском районе</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>28.07.2017</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>220759</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Козлов</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Герман</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Валентинович</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>г. Тула, п. Южный, ул. Лесная, д.5, кв. 4</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>4611</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>552775</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Московской области по городскому округу протвино</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>14.04.2012</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>431249</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>КОРОЛЬЧУК</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ЛЮБОВЬ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ВИТАЛЬЕВНА</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Тульская обл., Ленинский район,пос. Ильинка, ул. Центральная, д. 32, кв. 1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>913514</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ОУФМС РОССИИ ПО ТУЛЬСКОЙ ОБЛАСТИ В ЛЕНИНСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>16.05.2007</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>273289</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Косарева</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Лидия</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ивановна</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Тула ул. Галкина д.39 кв 107</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>345576</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Щекенским РУВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>08.11.2001</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>990768</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>КУЗНЕЦОВ</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ВАДИМ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>АЛЕКСЕЕВИЧ</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Октябьская д. 38 корп. 1 кв 8А</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>765224</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ОУФМС РОССИИ ПО ТУЛЬСКОЙ ОБЛАСИМ В ЗАРЕЧЕНСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>13.11.2017</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>990736</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ЛАГУТИНА</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>АНТОНИНА</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>НИКОЛАЕВНА</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Чаплыгина, д.5, кв. 8</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>058101</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Кировским отделением милиции УВД Пролетарского р-на гор. Тула</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>09.04.2003</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>431510</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Лгунов</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Геннадий</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>г. Тула ул. Мезенцев д.40 кв.28</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>255388</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Отделением в центральном рацонеотдела УФМС России по Тульской области в Туле</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>16.03.2011</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>757689</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Лифанова</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Алексеевна</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Тульская обл. г. Киреевск ул. Ленина д. 4 кв 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>045062</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Киреевским РОВД Тульской Области</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>10.01.2003</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>102248</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Лихорадова</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Валентина</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Геннадьевна</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Тульская область, г. Киреевск, ул. Тесакова, д. 4 кв8</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>7023</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>220898</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>08.11.2023</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>783836</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Макарова</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Светлана</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Тульская обл. г. Болохова ул. Соловцова д 19 А кв 44</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>737500</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Отделением УМВД России по Тульской области в Пролетарском Районе</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>06.07.2017</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>220542</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Мелехова</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Георгиевна</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>г. Тула. ул, Заварная, д. 125</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>731815</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД гор. Тулы 09.8.2005</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>432679</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Мелякова</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Татьяна</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>г. Тула М. Жукова д. 16 корп. 3 кв. 33</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>691247</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Привокзальным РОВД гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>29.03.2005</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>471189</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Моисеев</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Сергеевич</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>г. Тула ул. Ленина д. 6</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>106490</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>УВД Пролетарского района</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>17.04.2003</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>219957</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Морозов</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Федорович</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Тула, Скуратовский микрорайон, д. 4, кв. 1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>7007</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>912225</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Сруратовский ОМ УВД Центрального района города Тулы</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>12.04.2007</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>432594</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Морозова</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Тульская обл. г. Киреевс ул.Тесакова д. 12 кв. 49</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>258108</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Киреевским РОВД Тульской области</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>26.09.2001</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>345607</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>МОТОРИН</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ЮРИЙ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>НИКОЛАЕВИЧ</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>г. Тула, пос. Октябрьский, полезд 23-й, д.6</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>567695</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в зареченском районе</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>19.02.2015</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>024365</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>МЯЗИН</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ВЛАДИМИР</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ИВАНОВИЧ</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>г. Тула ПВС скуратовского о/м пос. угольный ул. подгорная д.6</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>400429</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Скуратовским о/м УВД Центрального района Тулы</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>05.03.2002</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>757800</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Никитина</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Галина</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Филипповна</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Галкина, д. 21, кв.152</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>942466</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>31.10.2002</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>431457</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Николаев</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Олег</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Тульская обл., г. Болохово, ул. Луговая, д. 45</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>147372</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ТП в Болохово ОУФМС России по Тульской обл.в Киреевском ройоне</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>31.10.2009</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>825560</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Никулина</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Тульская обл. Г. Киреевск мик Брусяновский д. 3 кв. 67</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>229826</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ТП в городе Липкм ОУФМС России по Тульской области в Киреевском районе 7010</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>345684</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Панферов</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>г.Тула ул Грибоедово д. 46</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>563318</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской обласи в Зареченском районе</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>24.03.2016</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>219617</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Печерский</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Туоьская обл. Щёкенский район, д. Лукино, ул. Новая , д.19 кв. 1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>7071</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>720823</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России по Тульской области в Щекинском районе</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>28.03.2017</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>219732</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Пикина</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Надежда</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Константиновна</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>г. Тула , Металлургов, д. 47Б, кв. 50</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>916160</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Кировским отделением милицииУВД Пролетарского района гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>26.11.2002</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>344207</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Пичкура</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Андрей</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Григорьевич</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>г. Тула, Хворостухина, д. 31</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>662739</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ТП В ПОС. ЛЕНИНСКИЙ ОТДЕЛ УФМС РОССИИ ПО ТУЛ. ОБЛ. В ЗАРЕЧЕНСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>27.06.2016</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>432441</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Поздняков</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Сергеевич</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Московская обл. г. Домодедово мик. Северный д. 62 к.1 кв.108</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>812187</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России по Московской обл. в Домодедовском районе</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>24.09.2009</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>234429</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Преснякова</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Марина</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Борисовна</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Тула , ул. Штыковая, 216А</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>577965</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Отделением УФМС России по Тульской области в зареченском районе</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>17.03.2015</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>010156</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Рублев</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Александр</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Серебровская, д.26, кв.110</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>7019</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>881765</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>УМВД России по Тульской области</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>23.04.2019</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>432642</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Рулева</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Галина</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>г.Тула, Проезд порошютный,д. 38б, кв. 52</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>627802</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в Привокзальгом районе</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>24.12.1970</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>219218</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Салий</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Тульская обл., Плавский район, пос. Белая Гора, д.20, кв.57</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>856253</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ОВД Плавского района Тульская область</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>27.05.1961</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>219648</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Сергеева</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Наталия</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Павловна</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>г. Тула ул. Кислородная д. 9</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>614072</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Кировским отделом Милиции УВД Пролетарского района гор. Тулы</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>13.07.2004</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>519517</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Симонян</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Самвел</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Жоржикович</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Тула , д. Марьино, д.88, кв. 6</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>566249</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России по Тульской области в Ленинском районе 26</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>432538</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Скачков</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Николаевич</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Тульская область Щекинский район д. Горячкино ул. Садовая д. 10 кв.6</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>7002</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>878229</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Советским отделом милиции Щекинского РУВД  Тульской области</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>16.10.2002</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>344194</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>СОБОЛЕВА</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>НАТАЛЬЯ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ВАСИЛЬЕВНА</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. М. Горького. д. 47, кв. 60</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>8703</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>903424</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>УВДВоркуты республика Коми</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>25.11.2003</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>431456</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Соломатин</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Иван</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Владимирович</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Тульсая обл., Веневсий р-он, с. Березово, ул. Придорожная, д.2, кв. 2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>7010</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>231644</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Отделением УФМС России по Тульской области в Веневском районе</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>13.12.2010</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>432765</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Соцкая</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Татьяна</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. М. Горького, д. 47, кв. 61</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>7005</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>733955</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Зареченским РОВД города Тулы</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>07.12.2005</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>432485</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Стебенева</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Лазаревна</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>г.Тула , ул. Кирова, д.184А. кв. 24</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>553897</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ОВД Воробьевского района Воронежской области</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>06.12.2005</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>431189</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Суркова</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Татьяна</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Тульская обл. г. Киреевск Л. Толстого д.17кв. 23</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>831615</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ОВД Киреевского Района Тульской области</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>27.11.2006</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>А</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>637159</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ТРОФИМОВА</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>НАТАЛИЯ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>НИКОЛАЕВНА</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>г. Тула, ул. Галкина, д. 20, кв.9</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>428749</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ОУФМС РОССИИ ПО ТУЛЬСКОЙ ОБЛАСТИ В ЗАРЕЧЕНСКОМ РАЙОНЕ</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>24.04.2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Туриянский</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Артем</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Александрович</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Тула, ул. Станиславского, д. 6, кв 60</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>418708</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ОУМВД России по Тульской области в центральном районе</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>15.05.2013</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>220358</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Федоров</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Владимир</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Станиславович</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Тульская обл., г. Киреевск,ул. Горняков,д. 11А, кв. 28</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>896739</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Кировсим отделом милиции УВД  Пролетарского р-на гор.Тулы</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>13.02.2007</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>431987</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Филичева</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Светлана</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Игоревна</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Тула , Перекопская, д. 7, кв. 53</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>667801</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ОУФМС России по Тульской области в центральном районе</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>27.06.2016</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>432496</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Ходырева</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Людмила</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Тула 2 -й пр. Металлургов д. 5 кв 98</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>110115</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ТП В МКН Кировский ОЙФМС России по Тульской обл. в пролетарском районе</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>24.04.2009</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>530381</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ЦЫБУЛЬСКИЙ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>НИКОЛАЙ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ДАВИДОВИЧ</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Тульская область, Щекинский район, с. Ломинцева,ул.Центральная,д.67</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>135390</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>УМВД Россиипо Тульской области</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>03.11.2022</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>219323</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Щербакова</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Сергеевна</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Тульская обл., Киреевский р-он, г. Липки, ул. Лесная, д. 1А, кв. 9</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>577628</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ТП В Г. ЛИПКИ ОУФМС РОССИИ ПО ТУЛЬ. ОБЛ. В КИРЕЕВСКОМ Р-НЕ</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>25.03.1970</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>218986</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ЯКОВЛЕВА</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ЛЮДМИЛА</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ВЯЧЕСЛАВОВНА</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>КАЛИНИНГРАЦКАЯ ОБЛ. Г. СВЕТЛОГОРСК УЛ. САДОВАЯ Д.2А КВ.1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>7009</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>100101</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ОУФМС ПО ТУЛЬСКОЙ ОБЛАСТИ В СОВЕТСКОМ РАЙОНЕ Г. ТУЛЫ</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>28.04.2009</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>991118</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Якубовский</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Сергей</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Евгеньевич</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>г. Тула. ул. Чапаево, д. 34, кв. 64</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>7014</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>577132</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Отделом УФМС России поТульской области в Пролетарском районе</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>31.03.2015</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Г</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>219935</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Воронков</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Василий</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Михайлович</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>город Тула, с. Глухие Поляны, ул. Лобачевского, д.46а</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>031151</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>УВД Центрального района города Тулы</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>23.04.2003</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>В</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>219518</t>
         </is>
       </c>
     </row>
